--- a/output/pdf_financials_xlsx/NEV.xlsx
+++ b/output/pdf_financials_xlsx/NEV.xlsx
@@ -1071,10 +1071,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>3e-06</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.001459</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -1089,16 +1089,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.005905</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.004764</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.0005</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000468</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>0</v>
@@ -1119,10 +1119,10 @@
         <v>0</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.005069</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0</v>
+        <v>0.005445</v>
       </c>
     </row>
     <row r="13">
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.998619</v>
+        <v>-1.998622</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.530777</v>
+        <v>-1.532236</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-1.067879</v>
@@ -2086,16 +2086,16 @@
         <v>-1.273496</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-2.519203</v>
+        <v>-2.513298</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-1.601249</v>
+        <v>-1.596485</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.08937100000000001</v>
+        <v>-0.08887100000000001</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-2.242182</v>
+        <v>-2.241714</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>-4.110936</v>
@@ -2116,10 +2116,10 @@
         <v>-2.730842</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-0.595476</v>
+        <v>-0.600545</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>-0.923382</v>
+        <v>-0.928827</v>
       </c>
     </row>
     <row r="28">
@@ -2190,10 +2190,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.992186</v>
+        <v>-1.992189</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.515571</v>
+        <v>-1.51703</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-1.053629</v>
@@ -2208,16 +2208,16 @@
         <v>-1.266303</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-2.515322</v>
+        <v>-2.509417</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-1.598438</v>
+        <v>-1.593674</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.08852</v>
+        <v>-0.08802</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-2.241338</v>
+        <v>-2.24087</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>-4.110112</v>
@@ -2238,10 +2238,10 @@
         <v>-2.730842</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-0.595476</v>
+        <v>-0.600545</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>-0.922909</v>
+        <v>-0.928354</v>
       </c>
     </row>
     <row r="30">
@@ -2513,19 +2513,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.254539</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.051939</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.06268</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.137739</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>1.013031</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>0.058074</v>
@@ -2543,10 +2543,10 @@
         <v>0.094913</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.431423</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.054528</v>
       </c>
       <c r="N34" s="1" t="inlineStr">
         <is>
@@ -2554,19 +2554,19 @@
         </is>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.072823</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>2.051791</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.221845</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.282458</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>1.087372</v>
       </c>
     </row>
     <row r="35">
@@ -2639,19 +2639,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.254539</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.051939</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.06268</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.137739</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>1.013031</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>0.058074</v>
@@ -2669,10 +2669,10 @@
         <v>0.094913</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.431423</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.054528</v>
       </c>
       <c r="N36" s="1" t="inlineStr">
         <is>
@@ -2680,19 +2680,19 @@
         </is>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.039443</v>
+        <v>0.112266</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.240356</v>
+        <v>2.292147</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0.11995</v>
+        <v>0.341795</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0.161388</v>
+        <v>0.443846</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0.06406299999999999</v>
+        <v>1.151435</v>
       </c>
     </row>
     <row r="37">
@@ -3425,10 +3425,10 @@
         <v>0.7831090000000001</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.806774</v>
+        <v>0.375351</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.198588</v>
+        <v>0.14406</v>
       </c>
       <c r="N48" s="1" t="inlineStr">
         <is>
@@ -3436,19 +3436,19 @@
         </is>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.108454</v>
+        <v>0.035631</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>2.182688</v>
+        <v>0.130897</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.377731</v>
+        <v>0.155886</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.304624</v>
+        <v>0.022166</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>1.098197</v>
+        <v>0.010825</v>
       </c>
     </row>
     <row r="49">
@@ -9088,7 +9088,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -16742,7 +16742,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E78" s="5" t="n">
@@ -36240,7 +36240,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -45616,7 +45616,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
@@ -47362,7 +47362,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
@@ -51378,7 +51378,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
@@ -53472,7 +53472,7 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
@@ -55684,7 +55684,7 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E456" s="5" t="n">
@@ -56610,7 +56610,7 @@
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E465" s="5" t="n">

--- a/output/pdf_financials_xlsx/NEV.xlsx
+++ b/output/pdf_financials_xlsx/NEV.xlsx
@@ -774,7 +774,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.019287</v>
+        <v>0.144696</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>0.218898</v>
@@ -789,16 +789,16 @@
         <v>0.45094</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.266497</v>
+        <v>0.291385</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.238543</v>
+        <v>0.35628</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.192443</v>
+        <v>0.300703</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.109898</v>
+        <v>0.252986</v>
       </c>
       <c r="O7" s="3" t="n">
         <v>0.289439</v>
@@ -896,31 +896,31 @@
         <v>0.490895</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.033286</v>
+        <v>0.278874</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.016736</v>
+        <v>0.214694</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0</v>
+        <v>0.068631</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0</v>
+        <v>0.045658</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0</v>
+        <v>0.133851</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>0</v>
+        <v>0.264453</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>0</v>
+        <v>0.416358</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>0</v>
+        <v>0.47172</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>0</v>
+        <v>0.049329</v>
       </c>
       <c r="O9" s="3" t="n">
         <v>0.066867</v>
@@ -963,7 +963,7 @@
         <v>1.15215</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.124093</v>
+        <v>0.192724</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>1.641776</v>
@@ -1024,7 +1024,7 @@
         <v>-1.15215</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-0.124093</v>
+        <v>-0.192724</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>-1.641776</v>
@@ -2600,16 +2600,16 @@
         <v>0</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>0</v>
+        <v>1.97914</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>0</v>
+        <v>0.711635</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>0</v>
+        <v>0.319752</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>0</v>
+        <v>0.099537</v>
       </c>
       <c r="N35" s="1" t="inlineStr">
         <is>
@@ -2663,16 +2663,16 @@
         <v>0.376054</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>1.015474</v>
+        <v>2.994614</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.094913</v>
+        <v>0.806548</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.431423</v>
+        <v>0.751175</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.054528</v>
+        <v>0.154065</v>
       </c>
       <c r="N36" s="1" t="inlineStr">
         <is>
@@ -2978,16 +2978,16 @@
         <v>0.008994</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0</v>
+        <v>0.187347</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>0</v>
+        <v>0.039179</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>0</v>
+        <v>0.024214</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>0</v>
+        <v>0.016697</v>
       </c>
       <c r="N41" s="1" t="inlineStr">
         <is>
@@ -3419,16 +3419,16 @@
         <v>0.121793</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>2.240899</v>
+        <v>0.07441200000000001</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.7831090000000001</v>
+        <v>0.032295</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.375351</v>
+        <v>0.031385</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.14406</v>
+        <v>0.027826</v>
       </c>
       <c r="N48" s="1" t="inlineStr">
         <is>
@@ -3725,22 +3725,22 @@
         <v>0.017292</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0</v>
+        <v>0.008279</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>0</v>
+        <v>0.004967</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>0</v>
+        <v>0.002899</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>0</v>
+        <v>0.002003</v>
       </c>
       <c r="K53" s="3" t="n">
-        <v>0</v>
+        <v>0.001094</v>
       </c>
       <c r="L53" s="3" t="n">
-        <v>0</v>
+        <v>0.000307</v>
       </c>
       <c r="M53" s="3" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
         <v>2.417087</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>0</v>
+        <v>2.557076</v>
       </c>
       <c r="H58" s="3" t="n">
         <v>2.893577</v>
@@ -4263,7 +4263,7 @@
         <v>0.020721</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>2.565355</v>
+        <v>0.008279</v>
       </c>
       <c r="H61" s="3" t="n">
         <v>0.004967</v>
@@ -4586,25 +4586,25 @@
         <v>0.003526</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0</v>
+        <v>0.146649</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>0</v>
+        <v>0.00122</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>0</v>
+        <v>0.024203</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>0</v>
+        <v>0.026258</v>
       </c>
       <c r="K66" s="3" t="n">
-        <v>0</v>
+        <v>0.002535</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>0</v>
+        <v>0.009722</v>
       </c>
       <c r="M66" s="3" t="n">
-        <v>0</v>
+        <v>0.007805</v>
       </c>
       <c r="N66" s="1" t="inlineStr">
         <is>
@@ -6018,25 +6018,25 @@
         <v>11.280453</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0</v>
+        <v>11.442253</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>0</v>
+        <v>15.082446</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0</v>
+        <v>15.185571</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>0</v>
+        <v>17.731285</v>
       </c>
       <c r="K88" s="3" t="n">
-        <v>0</v>
+        <v>18.090699</v>
       </c>
       <c r="L88" s="3" t="n">
-        <v>0</v>
+        <v>18.724555</v>
       </c>
       <c r="M88" s="3" t="n">
-        <v>0</v>
+        <v>19.13438</v>
       </c>
       <c r="N88" s="1" t="inlineStr">
         <is>
@@ -11472,7 +11472,11 @@
           <t>Marketable securities – Notes 5, 8 and 12</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>ShortTermInvestments</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
@@ -11576,7 +11580,11 @@
           <t>Receivables – Notes 4 and 12</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
@@ -11788,7 +11796,11 @@
           <t>Marketable securities – Note 5</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>ShortTermInvestments</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -11994,7 +12006,11 @@
           <t>Equipment – Note 7</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>MachineryFurnitureEquipment</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
@@ -12206,7 +12222,11 @@
           <t>Due to related parties – Note 12</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>OtherPayable</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>-</t>
@@ -12412,7 +12432,11 @@
           <t>Share capital – Note 10</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>-</t>
@@ -12708,7 +12732,11 @@
           <t>Receivables – Notes 4 and 11</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
@@ -12910,7 +12938,11 @@
           <t>Equipment – Note 6</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>MachineryFurnitureEquipment</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -13010,7 +13042,11 @@
           <t>Due to related parties – Note 11</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>OtherPayable</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -13322,7 +13358,11 @@
           <t>Marketable securities – Note 5</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>ShortTermInvestments</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
@@ -13832,7 +13872,11 @@
           <t>Receivables – Note 4</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>
@@ -14356,7 +14400,11 @@
           <t>Equipment – Note 5</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>MachineryFurnitureEquipment</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
@@ -14564,7 +14612,11 @@
           <t>Due to related parties – Note 9</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>OtherPayable</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>-</t>
@@ -14662,7 +14714,11 @@
           <t>Share capital – Note 7</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>-</t>
@@ -14964,7 +15020,11 @@
           <t>Exploration and evaluation assets – Notes 6 and 9</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -15068,7 +15128,11 @@
           <t>Receivables – Note 6</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>-</t>
@@ -15282,7 +15346,11 @@
           <t>Due from related parties – Note 8</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>OtherPayable</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>
@@ -15494,7 +15562,11 @@
           <t>Exploration and evaluations assets – Notes 6 and 8</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>-</t>
@@ -15598,7 +15670,11 @@
           <t>Due to related parties – Note 8</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>OtherPayable</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>
@@ -42236,7 +42312,11 @@
           <t>Consulting fees – Note 11</t>
         </is>
       </c>
-      <c r="D326" t="inlineStr"/>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E326" t="inlineStr">
         <is>
           <t>-</t>
@@ -42642,7 +42722,11 @@
           <t>Legal – Note 11</t>
         </is>
       </c>
-      <c r="D330" t="inlineStr"/>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E330" t="inlineStr">
         <is>
           <t>-</t>
@@ -42738,7 +42822,11 @@
           <t>Management fees – Note 11</t>
         </is>
       </c>
-      <c r="D331" t="inlineStr"/>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E331" t="inlineStr">
         <is>
           <t>-</t>
@@ -42842,7 +42930,11 @@
           <t>Rent – Note 11</t>
         </is>
       </c>
-      <c r="D332" t="inlineStr"/>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E332" t="inlineStr">
         <is>
           <t>-</t>
@@ -43560,7 +43652,11 @@
           <t>Depreciation – Note 7</t>
         </is>
       </c>
-      <c r="D339" t="inlineStr"/>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="E339" t="inlineStr">
         <is>
           <t>-</t>
@@ -43866,7 +43962,11 @@
           <t>Legal – Note 12</t>
         </is>
       </c>
-      <c r="D342" t="inlineStr"/>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E342" t="inlineStr">
         <is>
           <t>-</t>
@@ -43970,7 +44070,11 @@
           <t>Management fees – Note 12</t>
         </is>
       </c>
-      <c r="D343" t="inlineStr"/>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E343" t="inlineStr">
         <is>
           <t>-</t>
@@ -44172,7 +44276,11 @@
           <t>Rent – Note 12</t>
         </is>
       </c>
-      <c r="D345" t="inlineStr"/>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E345" t="inlineStr">
         <is>
           <t>-</t>
@@ -45102,7 +45210,11 @@
           <t>Depreciation – Note 6</t>
         </is>
       </c>
-      <c r="D354" t="inlineStr"/>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="E354" t="inlineStr">
         <is>
           <t>-</t>
@@ -46862,7 +46974,11 @@
           <t>Depreciation – Note 5</t>
         </is>
       </c>
-      <c r="D371" t="inlineStr"/>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="E371" t="inlineStr">
         <is>
           <t>-</t>
@@ -47562,7 +47678,11 @@
           <t>Legal – Note 9</t>
         </is>
       </c>
-      <c r="D378" t="inlineStr"/>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E378" t="inlineStr">
         <is>
           <t>-</t>
@@ -49794,7 +49914,11 @@
           <t>Consulting fees – Note 8</t>
         </is>
       </c>
-      <c r="D400" t="inlineStr"/>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E400" t="inlineStr">
         <is>
           <t>-</t>
@@ -49898,7 +50022,11 @@
           <t>Depreciation - Note 5</t>
         </is>
       </c>
-      <c r="D401" t="inlineStr"/>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="E401" t="inlineStr">
         <is>
           <t>-</t>
@@ -50214,7 +50342,11 @@
           <t>Professional fees – Note 8</t>
         </is>
       </c>
-      <c r="D404" t="inlineStr"/>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E404" t="inlineStr">
         <is>
           <t>-</t>
@@ -50422,7 +50554,11 @@
           <t>Salaries and benefits – Note 8</t>
         </is>
       </c>
-      <c r="D406" t="inlineStr"/>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E406" t="inlineStr">
         <is>
           <t>-</t>
